--- a/Portfolio_Dashboard_Output.xlsx
+++ b/Portfolio_Dashboard_Output.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.00&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,12 @@
     <font>
       <name val="Georgia"/>
       <color rgb="002F332E"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="00F1E9CB"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="6">
@@ -97,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -138,13 +144,10 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -730,7 +733,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I57"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -740,8 +743,8 @@
     <col width="28" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
-    <col width="65" customWidth="1" min="8" max="8"/>
-    <col width="65" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -772,7 +775,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>24291568.5</v>
+        <v>26132774.99</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -824,7 +827,7 @@
         <v>1159400</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4.772849476558091</v>
+        <v>4.43657438004061</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -837,7 +840,7 @@
         <v>762500</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>3.138949220179009</v>
+        <v>2.917791930982374</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -850,7 +853,7 @@
         <v>1306250</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>5.377380221454206</v>
+        <v>4.998512406355051</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -860,10 +863,10 @@
         </is>
       </c>
       <c r="B13" s="10" t="n">
-        <v>446250</v>
+        <v>1306620</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>1.837057166563781</v>
+        <v>4.999928252931396</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -873,10 +876,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>2709787.5</v>
+        <v>2613276.75</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>11.15525948849289</v>
+        <v>9.999997133867335</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -886,10 +889,10 @@
         </is>
       </c>
       <c r="B15" s="10" t="n">
-        <v>2534000</v>
+        <v>1741944</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>10.43160304778178</v>
+        <v>6.665744455636932</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -899,10 +902,10 @@
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>13927.5</v>
+        <v>1210739.24</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>0.05733470854300742</v>
+        <v>4.633029750814075</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -912,10 +915,10 @@
         </is>
       </c>
       <c r="B17" s="10" t="n">
-        <v>100831.5</v>
+        <v>711983.25</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>0.4150884698943998</v>
+        <v>2.724483910615877</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -928,7 +931,7 @@
         <v>1114646</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4.588612711443479</v>
+        <v>4.265318170100694</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -938,10 +941,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>688795</v>
+        <v>688881.75</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2.835531184410756</v>
+        <v>2.63608342498494</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -951,10 +954,10 @@
         </is>
       </c>
       <c r="B20" s="7" t="n">
-        <v>2300000</v>
+        <v>1742135</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>9.468305844474392</v>
+        <v>6.666475338599316</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -967,7 +970,7 @@
         <v>2612100</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>10.75311378102242</v>
+        <v>9.995494167762702</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -977,10 +980,10 @@
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>493081</v>
+        <v>1112299</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>2.029844223521425</v>
+        <v>4.256337110871821</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -993,7 +996,7 @@
         <v>6050000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>24.90576102568264</v>
+        <v>23.15100482943392</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1006,7 +1009,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>8.23330942997773</v>
+        <v>7.653224737002949</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1030,7 +1033,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>15.12623608475509</v>
+        <v>17.35280697030943</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1040,7 +1043,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>8.23330942997773</v>
+        <v>7.653224737002949</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1050,7 +1053,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>12.78295800454384</v>
+        <v>14.25183127863452</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1060,7 +1063,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>16.89244974032863</v>
+        <v>13.56787693368495</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1070,7 +1073,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>24.90576102568264</v>
+        <v>23.15100482943392</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1080,7 +1083,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>10.90402622621919</v>
+        <v>14.02325811706689</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1090,7 +1093,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>11.15525948849289</v>
+        <v>9.999997133867335</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1150,7 +1153,7 @@
         </is>
       </c>
       <c r="B41" s="13" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -1160,7 +1163,7 @@
         </is>
       </c>
       <c r="B42" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -1171,7 +1174,7 @@
       </c>
       <c r="B43" s="13" t="inlineStr">
         <is>
-          <t>79 / 100</t>
+          <t>100 / 100</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1186,7 @@
       </c>
       <c r="B44" s="12" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1215,351 +1218,80 @@
           <t>Excess %</t>
         </is>
       </c>
-      <c r="F47" s="3" t="inlineStr">
-        <is>
-          <t>Sell To Fix</t>
-        </is>
-      </c>
-      <c r="G47" s="3" t="inlineStr">
-        <is>
-          <t>Buy Elsewhere To Fix</t>
-        </is>
-      </c>
-      <c r="H47" s="14" t="inlineStr">
-        <is>
-          <t>Buy Candidates</t>
-        </is>
-      </c>
-      <c r="I47" s="14" t="inlineStr">
-        <is>
-          <t>Suggested Fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="36" customHeight="1">
-      <c r="A48" s="6" t="inlineStr">
-        <is>
-          <t>KCB</t>
-        </is>
-      </c>
-      <c r="B48" s="12" t="inlineStr">
-        <is>
-          <t>Banking</t>
-        </is>
-      </c>
-      <c r="C48" s="8" t="n">
-        <v>5.377380221454206</v>
-      </c>
-      <c r="D48" s="8" t="n">
-        <v>5</v>
-      </c>
-      <c r="E48" s="8" t="n">
-        <v>0.3773802214542057</v>
-      </c>
-      <c r="F48" s="12" t="inlineStr">
-        <is>
-          <t>KES 96,496.39</t>
-        </is>
-      </c>
-      <c r="G48" s="12" t="inlineStr">
-        <is>
-          <t>KES 1,833,431.50</t>
-        </is>
-      </c>
-      <c r="H48" s="15" t="inlineStr">
-        <is>
-          <t>CIC, Britam, VT</t>
-        </is>
-      </c>
-      <c r="I48" s="15" t="inlineStr">
-        <is>
-          <t>Sell KES 96,496.39 of KCB or buy KES 1,833,431.50 across CIC, Britam, VT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="36" customHeight="1">
-      <c r="A49" s="9" t="inlineStr">
-        <is>
-          <t>Safaricom</t>
-        </is>
-      </c>
-      <c r="B49" s="13" t="inlineStr">
-        <is>
-          <t>Telecom</t>
-        </is>
-      </c>
-      <c r="C49" s="11" t="n">
-        <v>11.15525948849289</v>
-      </c>
-      <c r="D49" s="11" t="n">
-        <v>10</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <v>1.155259488492888</v>
-      </c>
-      <c r="F49" s="13" t="inlineStr">
-        <is>
-          <t>KES 311,811.83</t>
-        </is>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>KES 2,806,306.50</t>
-        </is>
-      </c>
-      <c r="H49" s="16" t="inlineStr">
-        <is>
-          <t>CIC, Britam, NCBA</t>
-        </is>
-      </c>
-      <c r="I49" s="16" t="inlineStr">
-        <is>
-          <t>Sell KES 311,811.83 of Safaricom or buy KES 2,806,306.50 across CIC, Britam, NCBA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="36" customHeight="1">
-      <c r="A50" s="6" t="inlineStr">
-        <is>
-          <t>Jubilee</t>
-        </is>
-      </c>
-      <c r="B50" s="12" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="C50" s="8" t="n">
-        <v>10.43160304778178</v>
-      </c>
-      <c r="D50" s="8" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="E50" s="8" t="n">
-        <v>3.764936381115118</v>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>KES 979,887.96</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>KES 13,718,431.50</t>
-        </is>
-      </c>
-      <c r="H50" s="15" t="inlineStr">
-        <is>
-          <t>NCBA, VT, Kenya Power</t>
-        </is>
-      </c>
-      <c r="I50" s="15" t="inlineStr">
-        <is>
-          <t>Sell KES 979,887.96 of Jubilee or buy KES 13,718,431.50 across NCBA, VT, Kenya Power.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="36" customHeight="1">
-      <c r="A51" s="9" t="inlineStr">
-        <is>
-          <t>Total Energies Marketing</t>
-        </is>
-      </c>
-      <c r="B51" s="13" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="C51" s="11" t="n">
-        <v>9.468305844474392</v>
-      </c>
-      <c r="D51" s="11" t="n">
-        <v>6.666666666666667</v>
-      </c>
-      <c r="E51" s="11" t="n">
-        <v>2.801639177807725</v>
-      </c>
-      <c r="F51" s="13" t="inlineStr">
-        <is>
-          <t>KES 729,173.68</t>
-        </is>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>KES 10,208,431.50</t>
-        </is>
-      </c>
-      <c r="H51" s="16" t="inlineStr">
-        <is>
-          <t>CIC, Britam, NCBA</t>
-        </is>
-      </c>
-      <c r="I51" s="16" t="inlineStr">
-        <is>
-          <t>Sell KES 729,173.68 of Total Energies Marketing or buy KES 10,208,431.50 across CIC, Britam, NCBA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="36" customHeight="1">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>VOO / IVV</t>
-        </is>
-      </c>
-      <c r="B52" s="12" t="inlineStr">
-        <is>
-          <t>ETF</t>
-        </is>
-      </c>
-      <c r="C52" s="8" t="n">
-        <v>10.75311378102242</v>
-      </c>
-      <c r="D52" s="8" t="n">
-        <v>10</v>
-      </c>
-      <c r="E52" s="8" t="n">
-        <v>0.7531137810224156</v>
-      </c>
-      <c r="F52" s="12" t="inlineStr">
-        <is>
-          <t>KES 203,270.17</t>
-        </is>
-      </c>
-      <c r="G52" s="12" t="inlineStr">
-        <is>
-          <t>KES 1,829,431.50</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="inlineStr">
-        <is>
-          <t>CIC, Britam, NCBA</t>
-        </is>
-      </c>
-      <c r="I52" s="15" t="inlineStr">
-        <is>
-          <t>Sell KES 203,270.17 of VOO / IVV or buy KES 1,829,431.50 across CIC, Britam, NCBA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="36" customHeight="1"/>
-    <row r="54" ht="36" customHeight="1"/>
-    <row r="55" ht="36" customHeight="1">
-      <c r="A55" s="2" t="inlineStr">
+    </row>
+    <row r="48" ht="18" customHeight="1"/>
+    <row r="49" ht="18" customHeight="1"/>
+    <row r="50" ht="18" customHeight="1">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>Sector</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr">
+      <c r="B50" s="3" t="inlineStr">
         <is>
           <t>Sector Weight %</t>
         </is>
       </c>
-      <c r="C55" s="3" t="inlineStr">
+      <c r="C50" s="3" t="inlineStr">
         <is>
           <t>Limit %</t>
         </is>
       </c>
-      <c r="D55" s="3" t="inlineStr">
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>Excess %</t>
         </is>
       </c>
-      <c r="E55" s="3" t="inlineStr">
-        <is>
-          <t>Sell From Sector</t>
-        </is>
-      </c>
-      <c r="F55" s="3" t="inlineStr">
-        <is>
-          <t>Buy Outside Sector</t>
-        </is>
-      </c>
-      <c r="G55" s="3" t="inlineStr">
-        <is>
-          <t>Buy Candidates</t>
-        </is>
-      </c>
-      <c r="H55" s="14" t="inlineStr">
-        <is>
-          <t>Suggested Fix</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="36" customHeight="1">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Banking</t>
-        </is>
-      </c>
-      <c r="B56" s="8" t="n">
-        <v>22.62343073576915</v>
-      </c>
-      <c r="C56" s="8" t="n">
-        <v>20</v>
-      </c>
-      <c r="D56" s="8" t="n">
-        <v>2.623430735769148</v>
-      </c>
-      <c r="E56" s="12" t="inlineStr">
-        <is>
-          <t>KES 532,607.87</t>
-        </is>
-      </c>
-      <c r="F56" s="12" t="inlineStr">
-        <is>
-          <t>KES 2,130,431.50</t>
-        </is>
-      </c>
-      <c r="G56" s="12" t="inlineStr">
-        <is>
-          <t>CIC, Britam, VT</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="inlineStr">
-        <is>
-          <t>Sell KES 532,607.87 from Banking or buy KES 2,130,431.50 across CIC, Britam, VT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="36" customHeight="1">
-      <c r="A57" s="9" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
-        <v>25.26505368000634</v>
-      </c>
-      <c r="C57" s="11" t="n">
-        <v>20</v>
-      </c>
-      <c r="D57" s="11" t="n">
-        <v>5.265053680006339</v>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>KES 1,068,909.13</t>
-        </is>
-      </c>
-      <c r="F57" s="13" t="inlineStr">
-        <is>
-          <t>KES 4,275,636.50</t>
-        </is>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
-        <is>
-          <t>CIC, Britam, NCBA</t>
-        </is>
-      </c>
-      <c r="H57" s="16" t="inlineStr">
-        <is>
-          <t>Sell KES 1,068,909.13 from Energy or buy KES 4,275,636.50 across CIC, Britam, NCBA.</t>
+    </row>
+    <row r="51" ht="18" customHeight="1"/>
+    <row r="52" ht="18" customHeight="1">
+      <c r="A52" s="14" t="inlineStr">
+        <is>
+          <t>Holistic Rebalance Suggestion</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="18" customHeight="1">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C53" s="3" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="D53" s="3" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="F53" s="3" t="inlineStr">
+        <is>
+          <t>Estimated Value</t>
+        </is>
+      </c>
+      <c r="G53" s="15" t="inlineStr">
+        <is>
+          <t>Reason</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A52:G52"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>

--- a/Portfolio_Dashboard_Output.xlsx
+++ b/Portfolio_Dashboard_Output.xlsx
@@ -8,6 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="Dashboard1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Transactions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Portfolio_State" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -103,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -148,6 +150,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -775,7 +792,7 @@
         </is>
       </c>
       <c r="B4" s="5" t="n">
-        <v>26132774.99</v>
+        <v>27488881.84</v>
       </c>
     </row>
     <row r="5" ht="18" customHeight="1">
@@ -824,10 +841,10 @@
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>1159400</v>
+        <v>1125300</v>
       </c>
       <c r="C10" s="8" t="n">
-        <v>4.43657438004061</v>
+        <v>4.09365505133984</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -837,10 +854,10 @@
         </is>
       </c>
       <c r="B11" s="10" t="n">
-        <v>762500</v>
+        <v>1143750</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2.917791930982374</v>
+        <v>4.160773096036561</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -853,7 +870,7 @@
         <v>1306250</v>
       </c>
       <c r="C12" s="8" t="n">
-        <v>4.998512406355051</v>
+        <v>4.751921186183832</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -866,7 +883,7 @@
         <v>1306620</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>4.999928252931396</v>
+        <v>4.753267184912167</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -879,7 +896,7 @@
         <v>2613276.75</v>
       </c>
       <c r="C14" s="8" t="n">
-        <v>9.999997133867335</v>
+        <v>9.506668060238569</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -892,7 +909,7 @@
         <v>1741944</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>6.665744455636932</v>
+        <v>6.336903807652295</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -905,7 +922,7 @@
         <v>1210739.24</v>
       </c>
       <c r="C16" s="8" t="n">
-        <v>4.633029750814075</v>
+        <v>4.404468857799128</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -918,7 +935,7 @@
         <v>711983.25</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>2.724483910615877</v>
+        <v>2.590077159719058</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -931,7 +948,7 @@
         <v>1114646</v>
       </c>
       <c r="C18" s="8" t="n">
-        <v>4.265318170100694</v>
+        <v>4.054897563632585</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -941,10 +958,10 @@
         </is>
       </c>
       <c r="B19" s="10" t="n">
-        <v>688881.75</v>
+        <v>1593354.6</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2.63608342498494</v>
+        <v>5.796360176722271</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -957,7 +974,7 @@
         <v>1742135</v>
       </c>
       <c r="C20" s="8" t="n">
-        <v>6.666475338599316</v>
+        <v>6.337598634022868</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -967,10 +984,10 @@
         </is>
       </c>
       <c r="B21" s="10" t="n">
-        <v>2612100</v>
+        <v>2716584</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>9.995494167762702</v>
+        <v>9.882482728151594</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -983,7 +1000,7 @@
         <v>1112299</v>
       </c>
       <c r="C22" s="8" t="n">
-        <v>4.256337110871821</v>
+        <v>4.046359566293658</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -996,7 +1013,7 @@
         <v>6050000</v>
       </c>
       <c r="C23" s="11" t="n">
-        <v>23.15100482943392</v>
+        <v>22.00889812548301</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -1009,7 +1026,7 @@
         <v>2000000</v>
       </c>
       <c r="C24" s="8" t="n">
-        <v>7.653224737002949</v>
+        <v>7.275668801812565</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1"/>
@@ -1033,7 +1050,7 @@
         </is>
       </c>
       <c r="B28" s="8" t="n">
-        <v>17.35280697030943</v>
+        <v>17.7596165184724</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -1043,7 +1060,7 @@
         </is>
       </c>
       <c r="B29" s="11" t="n">
-        <v>7.653224737002949</v>
+        <v>7.275668801812565</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -1053,7 +1070,7 @@
         </is>
       </c>
       <c r="B30" s="8" t="n">
-        <v>14.25183127863452</v>
+        <v>13.92884229444525</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -1063,7 +1080,7 @@
         </is>
       </c>
       <c r="B31" s="11" t="n">
-        <v>13.56787693368495</v>
+        <v>16.18885637437772</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -1073,7 +1090,7 @@
         </is>
       </c>
       <c r="B32" s="8" t="n">
-        <v>23.15100482943392</v>
+        <v>22.00889812548301</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -1083,7 +1100,7 @@
         </is>
       </c>
       <c r="B33" s="11" t="n">
-        <v>14.02325811706689</v>
+        <v>13.33144982517048</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -1093,7 +1110,7 @@
         </is>
       </c>
       <c r="B34" s="8" t="n">
-        <v>9.999997133867335</v>
+        <v>9.506668060238569</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1"/>
@@ -1296,4 +1313,1426 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="16" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B1" s="16" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="C1" s="16" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D1" s="15" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="E1" s="15" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="F1" s="16" t="inlineStr">
+        <is>
+          <t>Broker</t>
+        </is>
+      </c>
+      <c r="G1" s="15" t="inlineStr">
+        <is>
+          <t>Fees</t>
+        </is>
+      </c>
+      <c r="H1" s="16" t="inlineStr">
+        <is>
+          <t>Benefits</t>
+        </is>
+      </c>
+      <c r="I1" s="15" t="inlineStr">
+        <is>
+          <t>Realized Gain</t>
+        </is>
+      </c>
+      <c r="J1" s="15" t="inlineStr">
+        <is>
+          <t>Unrealized Gain</t>
+        </is>
+      </c>
+      <c r="K1" s="15" t="inlineStr">
+        <is>
+          <t>Cost Basis</t>
+        </is>
+      </c>
+      <c r="L1" s="15" t="inlineStr">
+        <is>
+          <t>Average Purchase Price</t>
+        </is>
+      </c>
+      <c r="M1" s="15" t="inlineStr">
+        <is>
+          <t>Position Quantity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B2" s="17" t="inlineStr">
+        <is>
+          <t>Co-op Bank</t>
+        </is>
+      </c>
+      <c r="C2" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D2" s="18" t="n">
+        <v>34000</v>
+      </c>
+      <c r="E2" s="18" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="F2" s="17" t="inlineStr"/>
+      <c r="G2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H2" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I2" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="18" t="n">
+        <v>68000</v>
+      </c>
+      <c r="K2" s="18" t="n">
+        <v>1091400</v>
+      </c>
+      <c r="L2" s="18" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="M2" s="18" t="n">
+        <v>34000</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B3" s="19" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="C3" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D3" s="20" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E3" s="20" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="F3" s="19" t="inlineStr"/>
+      <c r="G3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I3" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="20" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K3" s="20" t="n">
+        <v>742500</v>
+      </c>
+      <c r="L3" s="20" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="M3" s="20" t="n">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>KCB</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="n">
+        <v>19000</v>
+      </c>
+      <c r="E4" s="18" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="F4" s="17" t="inlineStr"/>
+      <c r="G4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I4" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" s="18" t="n">
+        <v>38000</v>
+      </c>
+      <c r="K4" s="18" t="n">
+        <v>1268250</v>
+      </c>
+      <c r="L4" s="18" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="M4" s="18" t="n">
+        <v>19000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr">
+        <is>
+          <t>NCBA</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="n">
+        <v>14640</v>
+      </c>
+      <c r="E5" s="20" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="F5" s="19" t="inlineStr"/>
+      <c r="G5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I5" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="20" t="n">
+        <v>29280</v>
+      </c>
+      <c r="K5" s="20" t="n">
+        <v>1277340</v>
+      </c>
+      <c r="L5" s="20" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="M5" s="20" t="n">
+        <v>14640</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>Safaricom</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D6" s="18" t="n">
+        <v>80285</v>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="F6" s="17" t="inlineStr"/>
+      <c r="G6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I6" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>160570</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>2452706.75</v>
+      </c>
+      <c r="L6" s="18" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="M6" s="18" t="n">
+        <v>80285</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>Jubilee</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>4812</v>
+      </c>
+      <c r="E7" s="20" t="n">
+        <v>360</v>
+      </c>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="20" t="n">
+        <v>9624</v>
+      </c>
+      <c r="K7" s="20" t="n">
+        <v>1732320</v>
+      </c>
+      <c r="L7" s="20" t="n">
+        <v>360</v>
+      </c>
+      <c r="M7" s="20" t="n">
+        <v>4812</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>CIC</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D8" s="18" t="n">
+        <v>195596</v>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="F8" s="17" t="inlineStr"/>
+      <c r="G8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I8" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>391191.9999999999</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>819547.2400000001</v>
+      </c>
+      <c r="L8" s="18" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="M8" s="18" t="n">
+        <v>195596</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>Britam</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="n">
+        <v>47945</v>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="F9" s="19" t="inlineStr"/>
+      <c r="G9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>95890</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>616093.25</v>
+      </c>
+      <c r="L9" s="20" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="M9" s="20" t="n">
+        <v>47945</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>KenGen</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>99700</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="F10" s="17" t="inlineStr"/>
+      <c r="G10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>199400</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>915246</v>
+      </c>
+      <c r="L10" s="18" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="M10" s="18" t="n">
+        <v>99700</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>Kenya Power</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>39705</v>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="F11" s="19" t="inlineStr"/>
+      <c r="G11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>79410</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>609471.75</v>
+      </c>
+      <c r="L11" s="20" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>39705</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>Total Energies Marketing</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>30298</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="F12" s="17" t="inlineStr"/>
+      <c r="G12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>60596</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>1681539</v>
+      </c>
+      <c r="L12" s="18" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="M12" s="18" t="n">
+        <v>30298</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>VOO / IVV</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>50</v>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>52240</v>
+      </c>
+      <c r="F13" s="19" t="inlineStr"/>
+      <c r="G13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>2612000</v>
+      </c>
+      <c r="L13" s="20" t="n">
+        <v>52240</v>
+      </c>
+      <c r="M13" s="20" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>97</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>11465</v>
+      </c>
+      <c r="F14" s="17" t="inlineStr"/>
+      <c r="G14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>194</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>1112105</v>
+      </c>
+      <c r="L14" s="18" t="n">
+        <v>11465</v>
+      </c>
+      <c r="M14" s="18" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>Treasury Bonds</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>121</v>
+      </c>
+      <c r="E15" s="20" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F15" s="19" t="inlineStr"/>
+      <c r="G15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="19" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>6050000</v>
+      </c>
+      <c r="L15" s="20" t="n">
+        <v>50000</v>
+      </c>
+      <c r="M15" s="20" t="n">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:41:45</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>Money Market Fund</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="D16" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F16" s="17" t="inlineStr"/>
+      <c r="G16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17" t="inlineStr">
+        <is>
+          <t>Opening balance</t>
+        </is>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="L16" s="18" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="M16" s="18" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:46:00</t>
+        </is>
+      </c>
+      <c r="B17" s="19" t="inlineStr">
+        <is>
+          <t>Co-op Bank</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D17" s="20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E17" s="20" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F17" s="19" t="inlineStr"/>
+      <c r="G17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="19" t="inlineStr"/>
+      <c r="I17" s="20" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J17" s="20" t="n">
+        <v>66000</v>
+      </c>
+      <c r="K17" s="20" t="n">
+        <v>1059300</v>
+      </c>
+      <c r="L17" s="20" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="M17" s="20" t="n">
+        <v>33000</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:46:00</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="n">
+        <v>5000</v>
+      </c>
+      <c r="E18" s="18" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F18" s="17" t="inlineStr"/>
+      <c r="G18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="17" t="inlineStr"/>
+      <c r="I18" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="18" t="n">
+        <v>20000</v>
+      </c>
+      <c r="K18" s="18" t="n">
+        <v>1123750</v>
+      </c>
+      <c r="L18" s="18" t="n">
+        <v>74.91666666666667</v>
+      </c>
+      <c r="M18" s="18" t="n">
+        <v>15000</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:46:00</t>
+        </is>
+      </c>
+      <c r="B19" s="19" t="inlineStr">
+        <is>
+          <t>VOO / IVV</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D19" s="20" t="n">
+        <v>20</v>
+      </c>
+      <c r="E19" s="20" t="n">
+        <v>52242</v>
+      </c>
+      <c r="F19" s="19" t="inlineStr"/>
+      <c r="G19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="19" t="inlineStr"/>
+      <c r="I19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="20" t="n">
+        <v>100</v>
+      </c>
+      <c r="K19" s="20" t="n">
+        <v>3656840</v>
+      </c>
+      <c r="L19" s="20" t="n">
+        <v>52240.57142857143</v>
+      </c>
+      <c r="M19" s="20" t="n">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:50:37</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Kenya Power</t>
+        </is>
+      </c>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n">
+        <v>52131</v>
+      </c>
+      <c r="E20" s="18" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="F20" s="17" t="inlineStr"/>
+      <c r="G20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="17" t="inlineStr"/>
+      <c r="I20" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="18" t="n">
+        <v>79410</v>
+      </c>
+      <c r="K20" s="18" t="n">
+        <v>1513944.6</v>
+      </c>
+      <c r="L20" s="18" t="n">
+        <v>16.48530641578466</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <v>91836</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>2026-05-31 21:50:37</t>
+        </is>
+      </c>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>VOO / IVV</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="n">
+        <v>18</v>
+      </c>
+      <c r="E21" s="20" t="n">
+        <v>52242</v>
+      </c>
+      <c r="F21" s="19" t="inlineStr"/>
+      <c r="G21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="19" t="inlineStr"/>
+      <c r="I21" s="20" t="n">
+        <v>25.71428571431898</v>
+      </c>
+      <c r="J21" s="20" t="n">
+        <v>74.28571428544819</v>
+      </c>
+      <c r="K21" s="20" t="n">
+        <v>2716509.714285715</v>
+      </c>
+      <c r="L21" s="20" t="n">
+        <v>52240.57142857143</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <v>52</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Shares</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Buy Price</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Current Price</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Market Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Co-op Bank</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D2" t="n">
+        <v>32.1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>34.1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1125300</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>15000</v>
+      </c>
+      <c r="D3" t="n">
+        <v>74.25</v>
+      </c>
+      <c r="E3" t="n">
+        <v>76.25</v>
+      </c>
+      <c r="F3" t="n">
+        <v>1143750</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>KCB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>19000</v>
+      </c>
+      <c r="D4" t="n">
+        <v>66.75</v>
+      </c>
+      <c r="E4" t="n">
+        <v>68.75</v>
+      </c>
+      <c r="F4" t="n">
+        <v>1306250</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NCBA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>14640</v>
+      </c>
+      <c r="D5" t="n">
+        <v>87.25</v>
+      </c>
+      <c r="E5" t="n">
+        <v>89.25</v>
+      </c>
+      <c r="F5" t="n">
+        <v>1306620</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Safaricom</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Telecom</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>80285</v>
+      </c>
+      <c r="D6" t="n">
+        <v>30.55</v>
+      </c>
+      <c r="E6" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="F6" t="n">
+        <v>2613276.75</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Jubilee</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>4812</v>
+      </c>
+      <c r="D7" t="n">
+        <v>360</v>
+      </c>
+      <c r="E7" t="n">
+        <v>362</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1741944</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CIC</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>195596</v>
+      </c>
+      <c r="D8" t="n">
+        <v>4.19</v>
+      </c>
+      <c r="E8" t="n">
+        <v>6.19</v>
+      </c>
+      <c r="F8" t="n">
+        <v>1210739.24</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Britam</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>47945</v>
+      </c>
+      <c r="D9" t="n">
+        <v>12.85</v>
+      </c>
+      <c r="E9" t="n">
+        <v>14.85</v>
+      </c>
+      <c r="F9" t="n">
+        <v>711983.25</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>KenGen</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>99700</v>
+      </c>
+      <c r="D10" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="E10" t="n">
+        <v>11.18</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1114646</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kenya Power</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>91836</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15.35</v>
+      </c>
+      <c r="E11" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1593354.6</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Energies Marketing</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>30298</v>
+      </c>
+      <c r="D12" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="E12" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F12" t="n">
+        <v>1742135</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>VOO / IVV</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>52</v>
+      </c>
+      <c r="D13" t="n">
+        <v>52240</v>
+      </c>
+      <c r="E13" t="n">
+        <v>52242</v>
+      </c>
+      <c r="F13" t="n">
+        <v>2716584</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ETF</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>97</v>
+      </c>
+      <c r="D14" t="n">
+        <v>11465</v>
+      </c>
+      <c r="E14" t="n">
+        <v>11467</v>
+      </c>
+      <c r="F14" t="n">
+        <v>1112299</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Treasury Bonds</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Fixed Income</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>121</v>
+      </c>
+      <c r="D15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>6050000</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Money Market Fund</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>2</v>
+      </c>
+      <c r="D16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="E16" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="F16" t="n">
+        <v>2000000</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>